--- a/quizzes/021_regional_integration_challenges_quiz--quizzes.xlsx
+++ b/quizzes/021_regional_integration_challenges_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user_input_1</t>
+          <t>first_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>user_input_2</t>
+          <t>regional_integration_challenges</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>regional_integration_challenges_quiz_description</t>
+          <t>Regional Integration Challenges</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>user_input_3</t>
+          <t>obstacles</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>obstacles</t>
+          <t>Obstacles</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>user_input_4</t>
+          <t>training_programs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>training_programs</t>
+          <t>Training Programs</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,40 +607,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>user_input_5</t>
+          <t>obstacles_solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>classrooms</t>
+          <t>Obstacles' Solutions</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>user_input_6</t>
+          <t>regional_integration_obstacles</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>workshops</t>
+          <t>Regional Integration Obstacles</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>user_input_7</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>regional_integratio_n_obstacles</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>user_input_8</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>obstacles_details</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>user_input_9</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>regional_integration_obstacles</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>user_input_10</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>obstacles_solutions</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>user_input_11</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>regional_integration_obstacles</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>user_input_12</t>
+          <t>obstacles_solutions_note</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>obstacles_solutions</t>
+          <t>Obstacles Solutions Note</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>user_input_13</t>
+          <t>regional_integration_obstacles_note</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>regional_integratio_n_obstacles_solutions</t>
+          <t>Regional Integration Obstacles Note</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>user_input_14</t>
+          <t>additional_info_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>obstacles_solutions</t>
+          <t>Additional Information 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>user_input_15</t>
+          <t>additional_info_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Additional Information 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>user_input_16</t>
+          <t>additional_info_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Additional Information 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,207 +883,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>user_input_17</t>
+          <t>regional_integration_challenges_quiz_date</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Regional Integration Challenges Quiz Date</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>user_input_18</t>
+          <t>regional_integration_challenges_quiz_time</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Regional Integration Challenges Quiz Time</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>user_input_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>user_input_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>user_input_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>user_input_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>regional_integration_obstacles</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>user_input_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>regional_integration_obstacles</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>user_input_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>regional_integration_obstacles</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>user_input_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>regional_integration_obstacles</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,323 +965,136 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>user_input_3_choices</t>
+          <t>obstacles_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>user_input_3_choices</t>
+          <t>obstacles_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>user_input_3_choices</t>
+          <t>training_programs_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>user_input_4_choices</t>
+          <t>training_programs_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>user_input_4_choices</t>
+          <t>training_programs_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>user_input_4_choices</t>
+          <t>regional_integration_obstacles_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_6</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_6</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>user_input_5_choices</t>
+          <t>regional_integration_obstacles_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_7</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_7</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>user_input_5_choices</t>
+          <t>regional_integration_obstacles_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_8</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_8</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>user_input_5_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>option_9</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>option_9</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>user_input_6_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>user_input_6_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>user_input_22_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>option_22</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>option_22</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>user_input_22_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>option_23</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>option_23</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>user_input_22_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>option_24</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>option_24</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>user_input_23_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>option_25</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>option_25</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>user_input_23_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>option_26</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>option_26</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>user_input_23_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>option_27</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>option_27</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>user_input_24_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>user_input_24_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
